--- a/Data/IssuesSourceFiles/RCA_Data.xlsx
+++ b/Data/IssuesSourceFiles/RCA_Data.xlsx
@@ -28,13 +28,1902 @@
     <x:t>RCA</x:t>
   </x:si>
   <x:si>
+    <x:t>SWSUP-63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RE: Dolphin::Draft Changes_Lufax Holding Ltd_V2_XBRL_job ID_88899</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Medium</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{
+  "type": "doc",
+  "version": 1,
+  "content": [
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Hi Team,"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "We are now able to generate the output successfully. "
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "(Work Space ID :  20-F_12_2025_7)"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "RCA: The issue was caused by a start and end tag of the DescriptionOfAccountingPolicyForSharebasedPaymentTransactionsExplanatory element (Section Name : F43-F44). The tag has been removed, which resolved the issue."
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Regards,"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Sheikfareeth S"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "From: Vadivelan.S "
+        },
+        {
+          "type": "text",
+          "text": "vadivelan.s@dtracks.in",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:vadivelan.s@dtracks.in"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": " "
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "Sent: Friday,April 24,2026 00:05"
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "To: preprod@datatracks.com; 'Software Support'; 'IT-Helpdesk'"
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "Cc: 'USXBRLTL'; 'Muthukumaran V'; 'Rakesh T'; 'Cheirma Sakthi P'; 'Nagaraj V'; prakash.sudhakar@dtracks.in; sudhakar.p@dtracks.in; 'Usxbrlmanagers'; 'Softwareteam Dtracks'"
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "Subject: RE: Dolphin::Draft Changes_Lufax Holding Ltd_V2_XBRL_job ID_88899"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "+++ 'Softwareteam Dtracks' &lt;softwareteam@dtracks.in &lt;"
+        },
+        {
+          "type": "text",
+          "text": "softwareteam@dtracks.in",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:softwareteam@dtracks.in"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; &gt;"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Regards,"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Vadivelan S"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "www.datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "http://www.datatracks.com/",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "http://www.datatracks.com/"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; "
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "DataTracks Services Private Limited"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "(formerly TaurusQuest Services Private Limited)"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "ISO 9001:2015 certified for Quality"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "ISO 27001:2022 certified for Information Security"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Email: vadivelan.s@dtracks.in &lt;"
+        },
+        {
+          "type": "text",
+          "text": "vadivelan.s@dtracks.in",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:vadivelan.s@dtracks.in"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; "
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Work:+1 (609).257.4232 x 303  and +91.(44).40089000 x 303"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Mobile : +91-7550232370"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "From: preprod@datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "preprod@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:preprod@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt;  &lt;preprod@datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "preprod@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:preprod@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; &gt; "
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "Sent: 23 April 2026 23:23"
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "To: Software Support &lt;softwaresupport@datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "softwaresupport@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:softwaresupport@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; &gt;; IT-Helpdesk &lt;ithelpdesk@datatracks.net &lt;"
+        },
+        {
+          "type": "text",
+          "text": "ithelpdesk@datatracks.net",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:ithelpdesk@datatracks.net"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; &gt;"
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "Cc: USXBRLTL &lt;usxbrltl@datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "usxbrltl@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:usxbrltl@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; &gt;; Muthukumaran V &lt;muthukumaran@datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "muthukumaran@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:muthukumaran@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; &gt;; Rakesh T &lt;rakesh.t@datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "rakesh.t@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:rakesh.t@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; &gt;; Cheirma Sakthi P &lt;cheirmasakthi.p@datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "cheirmasakthi.p@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:cheirmasakthi.p@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; &gt;; preprod@datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "preprod@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:preprod@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; ; Nagaraj V &lt;nagaraj@datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "nagaraj@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:nagaraj@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; &gt;; prakash.sudhakar@dtracks.in &lt;"
+        },
+        {
+          "type": "text",
+          "text": "prakash.sudhakar@dtracks.in",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:prakash.sudhakar@dtracks.in"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; ; sudhakar.p@dtracks.in &lt;"
+        },
+        {
+          "type": "text",
+          "text": "sudhakar.p@dtracks.in",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:sudhakar.p@dtracks.in"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; ; Usxbrlmanagers &lt;usxbrlmanagers@datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "usxbrlmanagers@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:usxbrlmanagers@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; &gt;"
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "Subject: RE: Dolphin::Draft Changes_Lufax Holding Ltd_V2_XBRL_job ID_88899"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Hi Team,"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Please be informed that we are unable to download the output for the job mentioned below. Could you please rectify this issue as soon as possible."
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Thanks,"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Roja"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Team lead, Service Delivery, Publishing"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "DataTracks Global"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "&lt;"
+        },
+        {
+          "type": "text",
+          "text": "http://www.datatracks.com/",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "http://www.datatracks.com/"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; "
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "www.datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "http://www.datatracks.com/",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "http://www.datatracks.com/"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; "
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "+91 44 4008 9000, Ext: 203, 328"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "support@datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "support@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:support@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; "
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "This email and any attachments are confidential and intended only for the named recipient(s). If you are not the intended recipient, please notify the sender, delete it, and do not share or use its contents without written consent from DataTracks."
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "From: Sathish Kumar K. &lt;sathishkumar.k@datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "sathishkumar.k@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:sathishkumar.k@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; &gt; "
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "Sent: Thursday, April 23, 2026 3:29 AM"
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "To: Preprod@datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "Preprod@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:Preprod@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; "
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "Cc: USXBRLTL &lt;usxbrltl@datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "usxbrltl@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:usxbrltl@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; &gt;; Muthukumaran V &lt;muthukumaran@datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "muthukumaran@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:muthukumaran@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; &gt;; Cheirma Sakthi P &lt;cheirmasakthi.p@datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "cheirmasakthi.p@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:cheirmasakthi.p@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; &gt;"
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "Subject: Dolphin::Draft Changes_Lufax Holding Ltd_V2_XBRL_job ID_88899"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Hi Team,"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Please process draft edits with current document."
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Program"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Dolphin"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Filing Type"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "iXBRL"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Process Request"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Final Draft"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Process type"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Process Type as per previous Round"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Entity"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Lufax Holding Ltd"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "WS ID"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "20-F_12_2025_6"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Job id"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "88899"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Other Comments"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Preproduction ETA"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "04/23/26 10:00 AM IST"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Thanks,"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Sathish.K"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Team Lead, XBRL Services"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "DataTracks Global"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "&lt;"
+        },
+        {
+          "type": "text",
+          "text": "http://www.datatracks.com/",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "http://www.datatracks.com/"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; "
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "&lt;"
+        },
+        {
+          "type": "text",
+          "text": "http://www.datatracks.com/",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "http://www.datatracks.com/"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; www.datatracks.com"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "+044 4008 9000"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "This email and any attachments are confidential and intended only for the named recipient(s). If you are not the intended recipient, please notify the sender, delete it, and do not share or use its contents without written consent from DataTracks."
+        }
+      ]
+    }
+  ]
+}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SWSUP-59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dolphin |ATQC| CEF | V1 | PGIM Credit Income Fund | 150483</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{
+  "type": "doc",
+  "version": 1,
+  "content": [
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Hi Team,"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "RCA: LineItems is not created under the table in presentation tree which is causing this issue"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "RoleName :"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "N-2"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "N-2 - [Capital Stock]"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "N-2 - [Effects of Leverage]"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "N-2 - [Investment Objectives]"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "N-2 - [Long Term Debt]"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "N-2 - [Other Securities]"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "N-2 - [Outstanding Securities]"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "N-2 - [Risk Factors]"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "N-2 - [Senior Securities]"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Best Regards,"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Melbin Joe"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Ext : 317"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "&lt;"
+        },
+        {
+          "type": "text",
+          "text": "http://www.datatracksglobal.com/",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "http://www.datatracksglobal.com/"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; www.datatracksglobal.com"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "DataTracks Services Limited"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "(formerly TaurusQuest Services Private Limited)"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "ISO 9001:2015 certified for Quality"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "ISO 27001:2013 certified for Information Security"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "This e-mail and its attachments are confidential and solely for the intended addressee(s). Do not share or use them without DataTracks approval. If received in error, please advise the sender and delete the mail."
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "From: Preprod@datatracks.com "
+        },
+        {
+          "type": "text",
+          "text": "preprod@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:preprod@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": " "
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "Sent: 22 April 2026 06:49 AM"
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "To: Software Support &lt;softwaresupport@datatracks.com&gt;; IT-Helpdesk &lt;ithelpdesk@datatracks.net&gt;"
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "Cc: Muthukumaran V &lt;muthukumaran@datatracks.com&gt;; Nagaraj V &lt;nagaraj@datatracks.com&gt;; Rakesh T &lt;rakesh.t@datatracks.com&gt;; Cheirma Sakthi P &lt;cheirmasakthi.p@datatracks.com&gt;; USXBRLTL &lt;usxbrltl@datatracks.com&gt;; usxbrlteam &lt;usxbrlteam@dtracks.in&gt;; prakash.sudhakar@dtracks.in; Preprod@datatracks.com; sudhakar.p@dtracks.in; USXBRLTL &lt;usxbrltl@datatracks.com&gt;; Usxbrlmanagers &lt;usxbrlmanagers@datatracks.com&gt;"
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "Subject: Dolphin |ATQC| CEF | V1 | PGIM Credit Income Fund | 150483"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Hi Team,"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Please be informed that we are unable to download the output for the job mentioned below. Could you please rectify this issue as soon as possible."
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Kindly note: that the ETA for this job was 6:47 AM. We would be grateful for your prompt assistance in resolving this."
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Regards,"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Support Team"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "DataTracks Global"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "&lt;"
+        },
+        {
+          "type": "text",
+          "text": "http://www.datatracks.com/",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "http://www.datatracks.com/"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; "
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "&lt;"
+        },
+        {
+          "type": "text",
+          "text": "http://www.datatracks.com/",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "http://www.datatracks.com/"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; www.datatracks.com"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "+1 (201).882.6062"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "&lt;"
+        },
+        {
+          "type": "text",
+          "text": "support@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:support@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; support@datatracks.com"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "This email and any attachments are confidential and intended only for the named recipient(s). If you are not the intended recipient, please notify the sender, delete it, and do not share or use its contents without written consent from DataTracks."
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "From: prakash.sudhakar@dtracks.in &lt;"
+        },
+        {
+          "type": "text",
+          "text": "prakash.sudhakar@dtracks.in",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:prakash.sudhakar@dtracks.in"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt;  &lt;prakash.sudhakar@dtracks.in &lt;"
+        },
+        {
+          "type": "text",
+          "text": "prakash.sudhakar@dtracks.in",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:prakash.sudhakar@dtracks.in"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; &gt; "
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "Sent: Wednesday, April 22, 2026 5:04 AM"
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "To: Preprod@datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "Preprod@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:Preprod@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; "
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "Cc: USXBRLTL &lt;usxbrltl@datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "usxbrltl@datatracks.com",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:usxbrltl@datatracks.com"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; &gt;; usxbrlteam &lt;usxbrlteam@dtracks.in &lt;"
+        },
+        {
+          "type": "text",
+          "text": "usxbrlteam@dtracks.in",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:usxbrlteam@dtracks.in"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; &gt;"
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "Subject: Dolphin |ATQC| CEF | V1 | PGIM Credit Income Fund | 150483"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Hi Team,"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Kindly process the ATQC for the below entity in the mentioned workspace and attached input."
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Program"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Dolphin – CEF"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Filing Type"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "iXBRL"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Process Request"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "ATQC"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Process type"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "GCM-Merge"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Entity"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "PGIM Credit Income Fund"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "WS ID"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "N-2_04_2026_4"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Job id"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "150483"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Other Comments"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "URL: "
+        },
+        {
+          "type": "text",
+          "text": "http://10.9.9.68:1800/",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "http://10.9.9.68:1800/"
+              }
+            }
+          ]
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Preproduction ETA"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "04-22-26 6:47 AM"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "Regards,"
+        },
+        {
+          "type": "hardBreak"
+        },
+        {
+          "type": "text",
+          "text": "Prakash S"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "&lt;"
+        },
+        {
+          "type": "text",
+          "text": "http://www.datatracks.com/",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "http://www.datatracks.com/"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; "
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "www.datatracks.com &lt;"
+        },
+        {
+          "type": "text",
+          "text": "http://www.datatracks.com/",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "http://www.datatracks.com/"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; "
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "prakash.sudhakar@dtracks.in &lt;"
+        },
+        {
+          "type": "text",
+          "text": "prakash.sudhakar@dtracks.in",
+          "marks": [
+            {
+              "type": "link",
+              "attrs": {
+                "href": "mailto:prakash.sudhakar@dtracks.in"
+              }
+            }
+          ]
+        },
+        {
+          "type": "text",
+          "text": "&gt; "
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "+91 44 4008 9000, Ext: 207"
+        }
+      ]
+    },
+    {
+      "type": "paragraph",
+      "content": [
+        {
+          "type": "text",
+          "text": "This email and any attachments are confidential and intended only for the named recipient(s). If you are not the intended recipient, please notify the sender, delete it, and do not share or use its contents without written consent from DataTracks."
+        }
+      ]
+    }
+  ]
+}</x:t>
+  </x:si>
+  <x:si>
     <x:t>SWSUP-47</x:t>
   </x:si>
   <x:si>
     <x:t>RE: Output issue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Medium</x:t>
   </x:si>
   <x:si>
     <x:t>{
@@ -2769,7 +4658,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D5"/>
+  <x:dimension ref="A1:D7"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -2833,13 +4722,41 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:4">
+      <x:c r="A6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:4">
+      <x:c r="A7" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
